--- a/src/main/resources/шаблон.xlsx
+++ b/src/main/resources/шаблон.xlsx
@@ -19,19 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>СУММА(USD)</t>
-  </si>
-  <si>
-    <t>КУРС</t>
-  </si>
-  <si>
-    <t>СУММА(KZT)</t>
-  </si>
-  <si>
-    <t>НАЛОГ</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>ВИД (Купля/Продажа)</t>
   </si>
@@ -446,39 +434,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="10" width="19.5" customWidth="1"/>
+    <col min="1" max="4" width="19.5" customWidth="1"/>
+    <col min="5" max="5" width="29.33203125" customWidth="1"/>
+    <col min="6" max="10" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
